--- a/outputs/q4/q4_k2_k3_comparison.xlsx
+++ b/outputs/q4/q4_k2_k3_comparison.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9029098128200543</v>
+        <v>0.8825900780064836</v>
       </c>
       <c r="C13" t="n">
-        <v>1.190790358782802</v>
+        <v>1.183290165105396</v>
       </c>
     </row>
     <row r="14">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.805819625640109</v>
+        <v>1.765180156012967</v>
       </c>
       <c r="C14" t="n">
-        <v>2.538335928555482</v>
+        <v>2.522834443819205</v>
       </c>
     </row>
     <row r="15">
@@ -630,7 +630,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3186.338154658319</v>
+        <v>59776.33464387259</v>
       </c>
     </row>
     <row r="20">
@@ -682,7 +682,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>62450.32909684885</v>
+        <v>3728.020703809979</v>
       </c>
     </row>
     <row r="25">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>58722.30839303887</v>
+        <v>56589.99648921426</v>
       </c>
     </row>
     <row r="35">
